--- a/cotacoes/2026-09-08/fechamento/PEDIDO_BRASFARMA_09-09-2026.xlsx
+++ b/cotacoes/2026-09-08/fechamento/PEDIDO_BRASFARMA_09-09-2026.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -624,7 +624,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -679,7 +679,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.9% (aceito, lim 5%)</t>
+          <t>REAJUSTE +0.9% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -797,7 +797,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.0% (aceito, lim 5%)</t>
+          <t>REAJUSTE +3.0% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -1500,30 +1500,30 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1301</v>
+        <v>92221</v>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>7893454100647</t>
+          <t>7899620911352</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CETOBETA 20+0,64+2,5MG/G POM BG 30G</t>
+          <t>CETOCONAZOL 200MG CX 10 COMP</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>8.369999999999999</v>
+        <v>4.21</v>
       </c>
       <c r="I18" s="5">
         <f>G18*H18</f>
@@ -1534,13 +1534,13 @@
         <v/>
       </c>
       <c r="K18" s="5" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>7.69</v>
+        <v>4.1</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>7.69</v>
+        <v>4.1</v>
       </c>
       <c r="N18" s="6">
         <f>J18/M18-1</f>
@@ -1552,37 +1552,37 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.6% (aceito, lim 5%)</t>
+          <t>REAJUSTE +2.7% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>92221</v>
+        <v>608881</v>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>7899620911352</t>
+          <t>7898108640678</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CETOCONAZOL 200MG CX 10 COMP</t>
+          <t>CICATRISAN CURATIVO 10UN MICROPOROSO</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>4.21</v>
+        <v>1.89</v>
       </c>
       <c r="I19" s="5">
         <f>G19*H19</f>
@@ -1593,13 +1593,13 @@
         <v/>
       </c>
       <c r="K19" s="5" t="n">
-        <v>4.1</v>
+        <v>1.96</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>4.1</v>
+        <v>1.68</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>4.1</v>
+        <v>1.773333333333333</v>
       </c>
       <c r="N19" s="6">
         <f>J19/M19-1</f>
@@ -1611,24 +1611,24 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.7% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>608881</v>
+        <v>108901</v>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>7898108640678</t>
+          <t>7898216363445</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CICATRISAN CURATIVO 10UN MICROPOROSO</t>
+          <t>CLARITROMICINA 500MG CX 14 COMP REV</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -1641,7 +1641,7 @@
         <v>7</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>1.89</v>
+        <v>43.78</v>
       </c>
       <c r="I20" s="5">
         <f>G20*H20</f>
@@ -1652,13 +1652,13 @@
         <v/>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1.96</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1.68</v>
+        <v>43.94</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>1.773333333333333</v>
+        <v>43.94</v>
       </c>
       <c r="N20" s="6">
         <f>J20/M20-1</f>
@@ -1677,30 +1677,30 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>108901</v>
+        <v>1103</v>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>7898216363445</t>
+          <t>7898216361267</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CLARITROMICINA 500MG CX 14 COMP REV</t>
+          <t>CLARITROMICINA 500MG CX 7 COMP REV</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>43.78</v>
+        <v>24.32</v>
       </c>
       <c r="I21" s="5">
         <f>G21*H21</f>
@@ -1711,13 +1711,13 @@
         <v/>
       </c>
       <c r="K21" s="5" t="n">
-        <v>64.98999999999999</v>
+        <v>31.9</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>43.94</v>
+        <v>23.13</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>43.94</v>
+        <v>23.13</v>
       </c>
       <c r="N21" s="6">
         <f>J21/M21-1</f>
@@ -1729,37 +1729,33 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1103</v>
+        <v>129761</v>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>7898216361267</t>
-        </is>
-      </c>
+      <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CLARITROMICINA 500MG CX 7 COMP REV</t>
+          <t>CLORIDRATO DE BROMEXINA 1,6MG XPE FR 120ML+CM</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>24.32</v>
+        <v>6.44</v>
       </c>
       <c r="I22" s="5">
         <f>G22*H22</f>
@@ -1770,13 +1766,13 @@
         <v/>
       </c>
       <c r="K22" s="5" t="n">
-        <v>31.9</v>
+        <v>6.74</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>23.13</v>
+        <v>6.74</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>23.13</v>
+        <v>6.739999999999999</v>
       </c>
       <c r="N22" s="6">
         <f>J22/M22-1</f>
@@ -1795,13 +1791,17 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>129761</v>
+        <v>134601</v>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>7898060139951</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CLORIDRATO DE BROMEXINA 1,6MG XPE FR 120ML+CM</t>
+          <t>CLORIDRATO DE CICLOBENZAPRINA 10MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -1814,7 +1814,7 @@
         <v>4</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>6.44</v>
+        <v>5.28</v>
       </c>
       <c r="I23" s="5">
         <f>G23*H23</f>
@@ -1825,13 +1825,13 @@
         <v/>
       </c>
       <c r="K23" s="5" t="n">
-        <v>6.74</v>
+        <v>5.48</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>6.74</v>
+        <v>5.48</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>6.739999999999999</v>
+        <v>5.48</v>
       </c>
       <c r="N23" s="6">
         <f>J23/M23-1</f>
@@ -1843,37 +1843,37 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>134601</v>
+        <v>134661</v>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>7898060139951</t>
+          <t>7898060139913</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CLORIDRATO DE CICLOBENZAPRINA 10MG CX 30 COMP REV</t>
+          <t>CLORIDRATO DE CICLOBENZAPRINA 5MG CX 15 COMP REV</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>5.28</v>
+        <v>2.44</v>
       </c>
       <c r="I24" s="5">
         <f>G24*H24</f>
@@ -1884,13 +1884,13 @@
         <v/>
       </c>
       <c r="K24" s="5" t="n">
-        <v>5.48</v>
+        <v>2.53</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>5.48</v>
+        <v>2.53</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>5.48</v>
+        <v>2.53</v>
       </c>
       <c r="N24" s="6">
         <f>J24/M24-1</f>
@@ -1902,37 +1902,37 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>134661</v>
+        <v>135981</v>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>7898060139913</t>
+          <t>7898216360185</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CLORIDRATO DE CICLOBENZAPRINA 5MG CX 15 COMP REV</t>
+          <t>CLORIDRATO DE CIPROFLOXACINO 500MG CX 14 COMP REV</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>2.44</v>
+        <v>6.14</v>
       </c>
       <c r="I25" s="5">
         <f>G25*H25</f>
@@ -1943,13 +1943,13 @@
         <v/>
       </c>
       <c r="K25" s="5" t="n">
-        <v>2.53</v>
+        <v>6.19</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>2.53</v>
+        <v>5.99</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>2.53</v>
+        <v>6.116666666666667</v>
       </c>
       <c r="N25" s="6">
         <f>J25/M25-1</f>
@@ -1961,37 +1961,37 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>135981</v>
+        <v>152261</v>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>7898216360185</t>
+          <t>7898216360864</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CLORIDRATO DE CIPROFLOXACINO 500MG CX 14 COMP REV</t>
+          <t>CLORIDRATO DE LIDOCAINA 20MG/G GELEIA BG 30G</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>6.14</v>
+        <v>8.59</v>
       </c>
       <c r="I26" s="5">
         <f>G26*H26</f>
@@ -2002,13 +2002,13 @@
         <v/>
       </c>
       <c r="K26" s="5" t="n">
-        <v>6.19</v>
+        <v>8.93</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>5.99</v>
+        <v>8.77</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>6.116666666666667</v>
+        <v>8.876666666666667</v>
       </c>
       <c r="N26" s="6">
         <f>J26/M26-1</f>
@@ -2027,17 +2027,17 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>152261</v>
+        <v>644271</v>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>7898216360864</t>
+          <t>7897917006453</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CLORIDRATO DE LIDOCAINA 20MG/G GELEIA BG 30G</t>
+          <t>CLORIDRATO DE NAFAZOLINA 0,5MG/ML SOL NAS CT FR PLAS GOT X 30ML</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -2050,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>8.59</v>
+        <v>2.84</v>
       </c>
       <c r="I27" s="5">
         <f>G27*H27</f>
@@ -2061,13 +2061,13 @@
         <v/>
       </c>
       <c r="K27" s="5" t="n">
-        <v>8.93</v>
+        <v>2.72</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>8.77</v>
+        <v>2.72</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>8.876666666666667</v>
+        <v>2.72</v>
       </c>
       <c r="N27" s="6">
         <f>J27/M27-1</f>
@@ -2079,37 +2079,37 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +4.4% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>644271</v>
+        <v>171281</v>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>7897917006453</t>
+          <t>7898216362431</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CLORIDRATO DE NAFAZOLINA 0,5MG/ML SOL NAS CT FR PLAS GOT X 30ML</t>
+          <t>CLORIDRATO DE PROPANOLOL 40MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>2.84</v>
+        <v>2.13</v>
       </c>
       <c r="I28" s="5">
         <f>G28*H28</f>
@@ -2120,13 +2120,13 @@
         <v/>
       </c>
       <c r="K28" s="5" t="n">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="N28" s="6">
         <f>J28/M28-1</f>
@@ -2138,37 +2138,37 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.4% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +0.5% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>171281</v>
+        <v>92041</v>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>7898216362431</t>
+          <t>7898100241279</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CLORIDRATO DE PROPANOLOL 40MG CX 30 COMP</t>
+          <t>CONAZOL 20MG/G CREME BG 20G</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>2.13</v>
+        <v>3.86</v>
       </c>
       <c r="I29" s="5">
         <f>G29*H29</f>
@@ -2179,13 +2179,13 @@
         <v/>
       </c>
       <c r="K29" s="5" t="n">
-        <v>2.12</v>
+        <v>3.69</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>2.12</v>
+        <v>3.69</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>2.12</v>
+        <v>3.69</v>
       </c>
       <c r="N29" s="6">
         <f>J29/M29-1</f>
@@ -2197,37 +2197,37 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.5% (aceito, lim 5%)</t>
+          <t>REAJUSTE +4.6% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>92041</v>
+        <v>5003</v>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>7898100241279</t>
+          <t>7898108641989</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CONAZOL 20MG/G CREME BG 20G</t>
+          <t>CURATIVO MICKEY E MINNIE C/10 UND</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>3.86</v>
+        <v>2.71</v>
       </c>
       <c r="I30" s="5">
         <f>G30*H30</f>
@@ -2238,13 +2238,13 @@
         <v/>
       </c>
       <c r="K30" s="5" t="n">
-        <v>3.69</v>
+        <v>2.94</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>3.69</v>
+        <v>2.94</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>3.69</v>
+        <v>2.94</v>
       </c>
       <c r="N30" s="6">
         <f>J30/M30-1</f>
@@ -2256,37 +2256,37 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.6% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5003</v>
+        <v>203441</v>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>7898108641989</t>
+          <t>7894916145459</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CURATIVO MICKEY E MINNIE C/10 UND</t>
+          <t>DESLORATADINA 5MG CX 10 COMP REV</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>2.71</v>
+        <v>5.89</v>
       </c>
       <c r="I31" s="5">
         <f>G31*H31</f>
@@ -2297,13 +2297,13 @@
         <v/>
       </c>
       <c r="K31" s="5" t="n">
-        <v>2.94</v>
+        <v>6.79</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>2.94</v>
+        <v>6.79</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>2.94</v>
+        <v>6.79</v>
       </c>
       <c r="N31" s="6">
         <f>J31/M31-1</f>
@@ -2315,37 +2315,37 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>203441</v>
+        <v>214</v>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>7894916145459</t>
+          <t>7898216367016</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DESLORATADINA 5MG CX 10 COMP REV</t>
+          <t>DICLORIDRATO DE LEVOCETIRIZINA</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>5.89</v>
+        <v>7.73</v>
       </c>
       <c r="I32" s="5">
         <f>G32*H32</f>
@@ -2356,13 +2356,13 @@
         <v/>
       </c>
       <c r="K32" s="5" t="n">
-        <v>6.79</v>
+        <v>8.48</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>6.79</v>
+        <v>8.48</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>6.79</v>
+        <v>8.48</v>
       </c>
       <c r="N32" s="6">
         <f>J32/M32-1</f>
@@ -2374,37 +2374,37 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>214</v>
+        <v>229241</v>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>7898216367016</t>
+          <t>7894916145114</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DICLORIDRATO DE LEVOCETIRIZINA</t>
+          <t>DOMPERIDONA 10MG CX 2BL X 15 COMP</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>7.73</v>
+        <v>4.03</v>
       </c>
       <c r="I33" s="5">
         <f>G33*H33</f>
@@ -2415,13 +2415,13 @@
         <v/>
       </c>
       <c r="K33" s="5" t="n">
-        <v>8.48</v>
+        <v>4.19</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>8.48</v>
+        <v>4.19</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>8.48</v>
+        <v>4.19</v>
       </c>
       <c r="N33" s="6">
         <f>J33/M33-1</f>
@@ -2433,24 +2433,24 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>229241</v>
+        <v>648331</v>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>7894916145114</t>
+          <t>7898108640944</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DOMPERIDONA 10MG CX 2BL X 15 COMP</t>
+          <t>ESPARAD IMPERM SANFARMA 50MMX4,5M</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -2463,7 +2463,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>4.03</v>
+        <v>11.29</v>
       </c>
       <c r="I34" s="5">
         <f>G34*H34</f>
@@ -2474,13 +2474,13 @@
         <v/>
       </c>
       <c r="K34" s="5" t="n">
-        <v>4.19</v>
+        <v>11.4</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>4.19</v>
+        <v>11.4</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>4.19</v>
+        <v>11.4</v>
       </c>
       <c r="N34" s="6">
         <f>J34/M34-1</f>
@@ -2492,37 +2492,37 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>648331</v>
+        <v>645451</v>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>7898108640944</t>
+          <t>7898108641262</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ESPARAD IMPERM SANFARMA 50MMX4,5M</t>
+          <t>FITA MICROPOROSA SANFARMA 25MMX4,5M</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>11.29</v>
+        <v>3.89</v>
       </c>
       <c r="I35" s="5">
         <f>G35*H35</f>
@@ -2533,13 +2533,13 @@
         <v/>
       </c>
       <c r="K35" s="5" t="n">
-        <v>11.4</v>
+        <v>4.09</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>11.4</v>
+        <v>4.09</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>11.4</v>
+        <v>4.09</v>
       </c>
       <c r="N35" s="6">
         <f>J35/M35-1</f>
@@ -2551,37 +2551,37 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>645451</v>
+        <v>610041</v>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>7898108641262</t>
+          <t>7898719040195</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>FITA MICROPOROSA SANFARMA 25MMX4,5M</t>
+          <t>GELOFLAN BALSAMO AEROSSOL 120ML</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>3.89</v>
+        <v>11.99</v>
       </c>
       <c r="I36" s="5">
         <f>G36*H36</f>
@@ -2592,13 +2592,13 @@
         <v/>
       </c>
       <c r="K36" s="5" t="n">
-        <v>4.09</v>
+        <v>12.59</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>4.09</v>
+        <v>12.1</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>4.09</v>
+        <v>12.42666666666667</v>
       </c>
       <c r="N36" s="6">
         <f>J36/M36-1</f>
@@ -2610,37 +2610,33 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>648341</v>
+        <v>657281</v>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>7898108640982</t>
-        </is>
-      </c>
+      <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>FITA MICROPOROSA SANFARMA 50MMX4,5M</t>
+          <t>GLIBENCLAMIDA 5MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>6.39</v>
+        <v>1.47</v>
       </c>
       <c r="I37" s="5">
         <f>G37*H37</f>
@@ -2651,13 +2647,13 @@
         <v/>
       </c>
       <c r="K37" s="5" t="n">
-        <v>5.84</v>
+        <v>1.47</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>5.84</v>
+        <v>1.47</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>5.84</v>
+        <v>1.47</v>
       </c>
       <c r="N37" s="6">
         <f>J37/M37-1</f>
@@ -2669,37 +2665,37 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +9.4% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>610041</v>
+        <v>601411</v>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>7898719040195</t>
+          <t>7899620911833</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>GELOFLAN BALSAMO AEROSSOL 120ML</t>
+          <t>GLICENIX (N.S.) 1,37G CX 6 GLICEROL PED</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>11.99</v>
+        <v>5.53</v>
       </c>
       <c r="I38" s="5">
         <f>G38*H38</f>
@@ -2710,13 +2706,13 @@
         <v/>
       </c>
       <c r="K38" s="5" t="n">
-        <v>12.59</v>
+        <v>5.68</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>12.1</v>
+        <v>5.68</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>12.42666666666667</v>
+        <v>5.68</v>
       </c>
       <c r="N38" s="6">
         <f>J38/M38-1</f>
@@ -2728,33 +2724,33 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>657281</v>
+        <v>570021</v>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>GLIBENCLAMIDA 5MG CX 30 COMP</t>
+          <t>GUACOFLUS XAROPE 100ML</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>1.47</v>
+        <v>5.41</v>
       </c>
       <c r="I39" s="5">
         <f>G39*H39</f>
@@ -2765,13 +2761,13 @@
         <v/>
       </c>
       <c r="K39" s="5" t="n">
-        <v>1.47</v>
+        <v>5.66</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>1.47</v>
+        <v>5.66</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>1.47</v>
+        <v>5.66</v>
       </c>
       <c r="N39" s="6">
         <f>J39/M39-1</f>
@@ -2783,37 +2779,37 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>601411</v>
+        <v>531481</v>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>7899620911833</t>
+          <t>7894164005420</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>GLICENIX (N.S.) 1,37G CX 6 GLICEROL PED</t>
+          <t>HIDRALI 500ML LARANJA AIRELA</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>5.53</v>
+        <v>7.99</v>
       </c>
       <c r="I40" s="5">
         <f>G40*H40</f>
@@ -2824,13 +2820,13 @@
         <v/>
       </c>
       <c r="K40" s="5" t="n">
-        <v>5.68</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>5.68</v>
+        <v>7.97</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>5.68</v>
+        <v>8.19</v>
       </c>
       <c r="N40" s="6">
         <f>J40/M40-1</f>
@@ -2842,33 +2838,37 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>570021</v>
+        <v>306601</v>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>7894916141000</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>GUACOFLUS XAROPE 100ML</t>
+          <t>ITRACONAZOL 100MG CX 15 CAP</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>5.41</v>
+        <v>18.38</v>
       </c>
       <c r="I41" s="5">
         <f>G41*H41</f>
@@ -2879,13 +2879,13 @@
         <v/>
       </c>
       <c r="K41" s="5" t="n">
-        <v>5.66</v>
+        <v>17.49</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>5.66</v>
+        <v>17.49</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>5.66</v>
+        <v>17.49</v>
       </c>
       <c r="N41" s="6">
         <f>J41/M41-1</f>
@@ -2897,37 +2897,33 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.1% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>531481</v>
+        <v>584741</v>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>7894164005420</t>
-        </is>
-      </c>
+      <c r="C42" s="3" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>HIDRALI 500ML LARANJA AIRELA</t>
+          <t>LIMONADA PURGATIVA 175MG 200ML SUS</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>7.99</v>
+        <v>8.5</v>
       </c>
       <c r="I42" s="5">
         <f>G42*H42</f>
@@ -2938,13 +2934,13 @@
         <v/>
       </c>
       <c r="K42" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>7.97</v>
+        <v>8.06</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>8.19</v>
+        <v>8.526666666666666</v>
       </c>
       <c r="N42" s="6">
         <f>J42/M42-1</f>
@@ -2963,30 +2959,30 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>306601</v>
+        <v>616271</v>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>7894916141000</t>
+          <t>7894164010301</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>ITRACONAZOL 100MG CX 15 CAP</t>
+          <t>LORATADINA 1MG/ML 100ML XPE UN</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>18.38</v>
+        <v>5.66</v>
       </c>
       <c r="I43" s="5">
         <f>G43*H43</f>
@@ -2997,13 +2993,13 @@
         <v/>
       </c>
       <c r="K43" s="5" t="n">
-        <v>17.49</v>
+        <v>5.65</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>17.49</v>
+        <v>5.65</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>17.49</v>
+        <v>5.650000000000001</v>
       </c>
       <c r="N43" s="6">
         <f>J43/M43-1</f>
@@ -3015,33 +3011,37 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.1% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +0.2% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>584741</v>
+        <v>612321</v>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>7894164005734</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>LIMONADA PURGATIVA 175MG 200ML SUS</t>
+          <t>MAGMILK HORTELA 80MG/ML 100ML (HIDROXIDO</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>8.5</v>
+        <v>3.99</v>
       </c>
       <c r="I44" s="5">
         <f>G44*H44</f>
@@ -3052,13 +3052,13 @@
         <v/>
       </c>
       <c r="K44" s="5" t="n">
-        <v>8.76</v>
+        <v>4.14</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>8.06</v>
+        <v>4.14</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>8.526666666666666</v>
+        <v>4.14</v>
       </c>
       <c r="N44" s="6">
         <f>J44/M44-1</f>
@@ -3077,30 +3077,30 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>616271</v>
+        <v>542681</v>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>7894164010301</t>
+          <t>7894164005727</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>LORATADINA 1MG/ML 100ML XPE UN</t>
+          <t>MAGMILK TRADICIONAL 80MG/ML 100ML(ARL)</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>5.66</v>
+        <v>3.99</v>
       </c>
       <c r="I45" s="5">
         <f>G45*H45</f>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="K45" s="5" t="n">
-        <v>5.65</v>
+        <v>4.71</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>5.65</v>
+        <v>4.71</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>5.650000000000001</v>
+        <v>4.71</v>
       </c>
       <c r="N45" s="6">
         <f>J45/M45-1</f>
@@ -3129,37 +3129,33 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.2% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>612321</v>
+        <v>339301</v>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>7894164005734</t>
-        </is>
-      </c>
+      <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>MAGMILK HORTELA 80MG/ML 100ML (HIDROXIDO</t>
+          <t>MELOXICAM 15MG CX 10 COMP</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>3.99</v>
+        <v>2.05</v>
       </c>
       <c r="I46" s="5">
         <f>G46*H46</f>
@@ -3170,13 +3166,13 @@
         <v/>
       </c>
       <c r="K46" s="5" t="n">
-        <v>4.14</v>
+        <v>2.18</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>4.14</v>
+        <v>1.99</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>4.14</v>
+        <v>2.053333333333333</v>
       </c>
       <c r="N46" s="6">
         <f>J46/M46-1</f>
@@ -3188,37 +3184,37 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>542681</v>
+        <v>461901</v>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>7894164005727</t>
+          <t>7897917000741</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>MAGMILK TRADICIONAL 80MG/ML 100ML(ARL)</t>
+          <t>MICOSBEL 50MG/ML LOCAO FR 30ML</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>3.99</v>
+        <v>8.85</v>
       </c>
       <c r="I47" s="5">
         <f>G47*H47</f>
@@ -3229,13 +3225,13 @@
         <v/>
       </c>
       <c r="K47" s="5" t="n">
-        <v>4.71</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>4.71</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>4.71</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N47" s="6">
         <f>J47/M47-1</f>
@@ -3247,33 +3243,33 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>339301</v>
+        <v>360361</v>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="3" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG CX 10 COMP</t>
+          <t>NIFEDIPRESS 20MG CX 30 COMP RETARD</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>2.05</v>
+        <v>6.18</v>
       </c>
       <c r="I48" s="5">
         <f>G48*H48</f>
@@ -3284,13 +3280,13 @@
         <v/>
       </c>
       <c r="K48" s="5" t="n">
-        <v>2.18</v>
+        <v>6.22</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>1.99</v>
+        <v>6.22</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>2.053333333333333</v>
+        <v>6.22</v>
       </c>
       <c r="N48" s="6">
         <f>J48/M48-1</f>
@@ -3309,30 +3305,26 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>461901</v>
+        <v>220241</v>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>7897917000741</t>
-        </is>
-      </c>
+      <c r="C49" s="3" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>MICOSBEL 50MG/ML LOCAO FR 30ML</t>
+          <t>PEPSOGEL SUSP FR 240ML</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>8.85</v>
+        <v>11.69</v>
       </c>
       <c r="I49" s="5">
         <f>G49*H49</f>
@@ -3343,13 +3335,13 @@
         <v/>
       </c>
       <c r="K49" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>11.66</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>11.38</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>11.38</v>
       </c>
       <c r="N49" s="6">
         <f>J49/M49-1</f>
@@ -3361,33 +3353,37 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +0.3% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>360361</v>
+        <v>404881</v>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
-      <c r="C50" s="3" t="inlineStr"/>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>7898216362189</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>NIFEDIPRESS 20MG CX 30 COMP RETARD</t>
+          <t>PIROXICAM 20MG CX 10 CAP</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>6.18</v>
+        <v>4.22</v>
       </c>
       <c r="I50" s="5">
         <f>G50*H50</f>
@@ -3398,13 +3394,13 @@
         <v/>
       </c>
       <c r="K50" s="5" t="n">
-        <v>6.22</v>
+        <v>4.15</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>6.22</v>
+        <v>4.15</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>6.22</v>
+        <v>4.15</v>
       </c>
       <c r="N50" s="6">
         <f>J50/M50-1</f>
@@ -3416,33 +3412,37 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +1.7% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>220241</v>
+        <v>408801</v>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
-      <c r="C51" s="3" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>7894916141123</t>
+        </is>
+      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>PEPSOGEL SUSP FR 240ML</t>
+          <t>PREDNISONA 20MG CX 10 COMP</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>11.69</v>
+        <v>1.36</v>
       </c>
       <c r="I51" s="5">
         <f>G51*H51</f>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="K51" s="5" t="n">
-        <v>11.66</v>
+        <v>5.04</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>11.38</v>
+        <v>5.04</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>11.38</v>
+        <v>5.04</v>
       </c>
       <c r="N51" s="6">
         <f>J51/M51-1</f>
@@ -3471,24 +3471,28 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.3% (aceito, lim 5%)</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>conferir emb.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>565861</v>
+        <v>483381</v>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>7898100244669</t>
+          <t>7899620912144</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>PHITOSS KIDS 7MG/ML XPE 100ML</t>
+          <t>PREDNISONA 20MG CX 20 COMP</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
@@ -3501,7 +3505,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>6.05</v>
+        <v>6.71</v>
       </c>
       <c r="I52" s="5">
         <f>G52*H52</f>
@@ -3512,13 +3516,13 @@
         <v/>
       </c>
       <c r="K52" s="5" t="n">
-        <v>5.66</v>
+        <v>6.97</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>5.66</v>
+        <v>6.69</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>5.66</v>
+        <v>6.783333333333334</v>
       </c>
       <c r="N52" s="6">
         <f>J52/M52-1</f>
@@ -3530,37 +3534,37 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +6.9% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>404881</v>
+        <v>414621</v>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>7898216362189</t>
+          <t>7895296210324</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>PIROXICAM 20MG CX 10 CAP</t>
+          <t>PROPIONATO DE CLOBETASOL 0,5MG/G CREME DERM BG 30G</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>4.22</v>
+        <v>6.41</v>
       </c>
       <c r="I53" s="5">
         <f>G53*H53</f>
@@ -3571,13 +3575,13 @@
         <v/>
       </c>
       <c r="K53" s="5" t="n">
-        <v>4.15</v>
+        <v>6.19</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>4.15</v>
+        <v>6.19</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>4.15</v>
+        <v>6.19</v>
       </c>
       <c r="N53" s="6">
         <f>J53/M53-1</f>
@@ -3589,37 +3593,37 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.7% (aceito, lim 5%)</t>
+          <t>REAJUSTE +3.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>408801</v>
+        <v>667251</v>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>7894916141123</t>
+          <t>7898216366088</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>PREDNISONA 20MG CX 10 COMP</t>
+          <t>ROSUVASTATINA CALCICA 5MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>1.36</v>
+        <v>5.86</v>
       </c>
       <c r="I54" s="5">
         <f>G54*H54</f>
@@ -3630,13 +3634,13 @@
         <v/>
       </c>
       <c r="K54" s="5" t="n">
-        <v>5.04</v>
+        <v>5.9</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>5.04</v>
+        <v>5.9</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>5.04</v>
+        <v>5.900000000000001</v>
       </c>
       <c r="N54" s="6">
         <f>J54/M54-1</f>
@@ -3648,41 +3652,37 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>conferir emb.</t>
-        </is>
-      </c>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>483381</v>
+        <v>431481</v>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>7899620912144</t>
+          <t>7899620911857</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>PREDNISONA 20MG CX 20 COMP</t>
+          <t>SECNIDAZOL 1000MG CX 2 COMP</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>6.71</v>
+        <v>2.55</v>
       </c>
       <c r="I55" s="5">
         <f>G55*H55</f>
@@ -3693,13 +3693,13 @@
         <v/>
       </c>
       <c r="K55" s="5" t="n">
-        <v>6.97</v>
+        <v>2.65</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>6.69</v>
+        <v>2.16</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>6.783333333333334</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="N55" s="6">
         <f>J55/M55-1</f>
@@ -3718,30 +3718,30 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>414621</v>
+        <v>538261</v>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>7895296210324</t>
+          <t>7894164005611</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>PROPIONATO DE CLOBETASOL 0,5MG/G CREME DERM BG 30G</t>
+          <t>SILUSGEL SUS 100ML</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>6.41</v>
+        <v>7.62</v>
       </c>
       <c r="I56" s="5">
         <f>G56*H56</f>
@@ -3752,13 +3752,13 @@
         <v/>
       </c>
       <c r="K56" s="5" t="n">
-        <v>6.19</v>
+        <v>7.68</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>6.19</v>
+        <v>7.63</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>6.19</v>
+        <v>7.663333333333333</v>
       </c>
       <c r="N56" s="6">
         <f>J56/M56-1</f>
@@ -3770,37 +3770,37 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.6% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>315361</v>
+        <v>436201</v>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>7896004720838</t>
+          <t>7899620911079</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>REPOFLOR 200MG FR 6 CAP</t>
+          <t>SINVASTATINA 40MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>23.64</v>
+        <v>5.53</v>
       </c>
       <c r="I57" s="5">
         <f>G57*H57</f>
@@ -3811,13 +3811,13 @@
         <v/>
       </c>
       <c r="K57" s="5" t="n">
-        <v>21.536</v>
+        <v>5.79</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>14.14</v>
+        <v>5.79</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>19.07066666666667</v>
+        <v>5.79</v>
       </c>
       <c r="N57" s="6">
         <f>J57/M57-1</f>
@@ -3829,37 +3829,37 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +9.8% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>667251</v>
+        <v>82461</v>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>7898216366088</t>
+          <t>7893454100685</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>ROSUVASTATINA CALCICA 5MG CX 30 COMP REV</t>
+          <t>TANDENE 125+50+300+30MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>5.86</v>
+        <v>7.98</v>
       </c>
       <c r="I58" s="5">
         <f>G58*H58</f>
@@ -3870,13 +3870,13 @@
         <v/>
       </c>
       <c r="K58" s="5" t="n">
-        <v>5.9</v>
+        <v>7.95</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>5.9</v>
+        <v>7.95</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>5.900000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="N58" s="6">
         <f>J58/M58-1</f>
@@ -3888,37 +3888,33 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +0.4% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>431481</v>
+        <v>394941</v>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>7899620911857</t>
-        </is>
-      </c>
+      <c r="C59" s="3" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>SECNIDAZOL 1000MG CX 2 COMP</t>
+          <t>TYFLEN (N.S.) 100MG/ML SUS FR 15ML BEBE</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>2.55</v>
+        <v>4.39</v>
       </c>
       <c r="I59" s="5">
         <f>G59*H59</f>
@@ -3929,13 +3925,13 @@
         <v/>
       </c>
       <c r="K59" s="5" t="n">
-        <v>2.65</v>
+        <v>4.2</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>2.466666666666667</v>
+        <v>4.2</v>
       </c>
       <c r="N59" s="6">
         <f>J59/M59-1</f>
@@ -3947,317 +3943,26 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +4.5% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>538261</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr"/>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>7894164005611</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>SILUSGEL SUS 100ML</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="I60" s="5">
-        <f>G60*H60</f>
-        <v/>
-      </c>
-      <c r="J60" s="5">
-        <f>H60/E60</f>
-        <v/>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>7.663333333333333</v>
-      </c>
-      <c r="N60" s="6">
-        <f>J60/M60-1</f>
-        <v/>
-      </c>
-      <c r="O60" s="6">
-        <f>J60/K60-1</f>
-        <v/>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>436201</v>
-      </c>
-      <c r="B61" s="2" t="inlineStr"/>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>7899620911079</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>SINVASTATINA 40MG CX 30 COMP REV</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G61" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="I61" s="5">
-        <f>G61*H61</f>
-        <v/>
-      </c>
-      <c r="J61" s="5">
-        <f>H61/E61</f>
-        <v/>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="N61" s="6">
-        <f>J61/M61-1</f>
-        <v/>
-      </c>
-      <c r="O61" s="6">
-        <f>J61/K61-1</f>
-        <v/>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="I60" s="8">
+        <f>SUM(I2:I59)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>201</v>
-      </c>
-      <c r="B62" s="2" t="inlineStr"/>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>7893454100678</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>TANDENE 125+50+300+30MG CX 15 COMP</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="I62" s="5">
-        <f>G62*H62</f>
-        <v/>
-      </c>
-      <c r="J62" s="5">
-        <f>H62/E62</f>
-        <v/>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>3.776666666666667</v>
-      </c>
-      <c r="N62" s="6">
-        <f>J62/M62-1</f>
-        <v/>
-      </c>
-      <c r="O62" s="6">
-        <f>J62/K62-1</f>
-        <v/>
-      </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +4.1% (aceito, lim 5%)</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>82461</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr"/>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>7893454100685</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>TANDENE 125+50+300+30MG CX 30 COMP</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="I63" s="5">
-        <f>G63*H63</f>
-        <v/>
-      </c>
-      <c r="J63" s="5">
-        <f>H63/E63</f>
-        <v/>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="N63" s="6">
-        <f>J63/M63-1</f>
-        <v/>
-      </c>
-      <c r="O63" s="6">
-        <f>J63/K63-1</f>
-        <v/>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +0.4% (aceito, lim 5%)</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>394941</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" s="3" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>TYFLEN (N.S.) 100MG/ML SUS FR 15ML BEBE</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G64" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="I64" s="5">
-        <f>G64*H64</f>
-        <v/>
-      </c>
-      <c r="J64" s="5">
-        <f>H64/E64</f>
-        <v/>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N64" s="6">
-        <f>J64/M64-1</f>
-        <v/>
-      </c>
-      <c r="O64" s="6">
-        <f>J64/K64-1</f>
-        <v/>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +4.5% (aceito, lim 5%)</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="I65" s="8">
-        <f>SUM(I2:I64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>Pedido FINAL BRASFARMA — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: preço até 5% acima da referência (últ. compra; sem ela, menor histórico), 10% quando o item está zerado. 'Qtd pedido' na embalagem do fornecedor.</t>
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Pedido FINAL BRASFARMA — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: teto de reajuste de 4% sobre a última compra OU 6% sobre a média histórica (3/6/12m). 'Qtd pedido' na embalagem do fornecedor.</t>
         </is>
       </c>
     </row>
